--- a/config/scene_story_choices.xlsx
+++ b/config/scene_story_choices.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="scene_story_choices" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="scene_story_choices" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>金のリンゴ</t>
+          <t>金苹果</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1198,7 +1198,6 @@
           <t>Golden Apple</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>황금 사과</t>
@@ -1223,7 +1222,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>銀のリンゴ</t>
+          <t>银苹果</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1236,7 +1235,6 @@
           <t>Silver Apple</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>실버 사과</t>
@@ -1261,7 +1259,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>腐ったリンゴ</t>
+          <t>烂苹果</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1274,7 +1272,6 @@
           <t>Rotten Apple</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>썩은 사과</t>
@@ -1292,14 +1289,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1309,7 +1299,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>金のリンゴ2</t>
+          <t>金苹果2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1322,7 +1312,6 @@
           <t>Golden Apple II</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>황금 사과2</t>
@@ -1347,7 +1336,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>銀のリンゴ2</t>
+          <t>银苹果2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1360,7 +1349,6 @@
           <t>Silver Apple II</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>실버 사과2</t>
@@ -1385,7 +1373,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>腐ったリンゴ2</t>
+          <t>烂苹果2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1398,7 +1386,6 @@
           <t>Rotten Apple II</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>썩은 사과2</t>
@@ -1416,14 +1403,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1433,7 +1413,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>左に行く</t>
+          <t>向左走</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1446,7 +1426,6 @@
           <t>Go left</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>왼쪽 가기</t>
@@ -1471,7 +1450,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>右に行く</t>
+          <t>向右走</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1484,7 +1463,6 @@
           <t>Go right</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>오른쪽 가기</t>
@@ -1495,17 +1473,9 @@
           <t>100009</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1515,7 +1485,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>出てこい！{0}！水で解凍しよう！</t>
+          <t>出来！{0}!用水解冻！</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1528,7 +1498,6 @@
           <t>Come forth, {0}! Use water to melt the ice!</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>나와라! 꼬부기! 물로 해동!</t>
@@ -1539,7 +1508,6 @@
           <t>100105</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1549,7 +1517,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>出てこい！{0}！水で解凍しよう！</t>
+          <t>出来！{0}!用水解冻！</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1562,7 +1530,6 @@
           <t>Come forth, {0}! Use water to melt the ice!</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>나와라! 파이리! 불꽃로 해동!</t>
@@ -1580,14 +1547,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" s="1" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1597,7 +1557,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>{0}を優先治癒</t>
+          <t>优先治疗{0}</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1610,7 +1570,6 @@
           <t>Prioritize healing {0}</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>빈티나를 우선 치료</t>
@@ -1635,7 +1594,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>不良少年を先に追い出す</t>
+          <t>先把不良少年赶出去</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1648,7 +1607,6 @@
           <t>Drive off the thugs first</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>불량 소년을 우선적으로 쫓아내다</t>
